--- a/src/test/resources/TestDriver/Hearst_ROA/ActivityData/ROA_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_ROA/ActivityData/ROA_AP.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>standalone_price_policy</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>parent_child</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parent_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -458,6 +468,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +493,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,6 +518,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_CAN_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +548,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_CAN_New_60</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,6 +578,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,6 +603,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_CAN_Renew_85</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -578,6 +633,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_CAN_Renew_85</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -598,6 +663,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -618,6 +688,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_GIFT_US_4999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -638,6 +718,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_GIFT_US_4999</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -658,6 +748,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -678,6 +773,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_CAN_Renew_70</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -698,6 +803,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_CAN_Renew_70</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -718,6 +833,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -738,6 +858,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_CAN_Renew_85</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,6 +888,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_CAN_Renew_85</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -778,6 +918,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -798,6 +943,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_US_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -818,6 +973,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_US_Renew_50</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -838,6 +1003,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -858,6 +1028,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_US_Renew_60</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -878,6 +1058,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_US_Renew_60</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -898,6 +1088,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -918,6 +1113,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -938,6 +1143,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_MGRT_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -958,6 +1173,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -978,6 +1198,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_New_45</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -998,6 +1228,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_New_45</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1018,6 +1258,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1038,6 +1283,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_New_4999</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1058,6 +1313,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_New_4999</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1078,6 +1343,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1098,6 +1368,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1118,6 +1398,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_New_50</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1138,6 +1428,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1158,6 +1453,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1178,6 +1483,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ROA_PRTDIG_US_Renew_75</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1198,6 +1513,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1216,6 +1536,11 @@
       <c r="D40" t="inlineStr">
         <is>
           <t>DOLLAR_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Parent</t>
         </is>
       </c>
     </row>
